--- a/data/stats/supp_tables/fallcover-cc-cc-estimates.xlsx
+++ b/data/stats/supp_tables/fallcover-cc-cc-estimates.xlsx
@@ -393,10 +393,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3202159858169036</v>
+        <v>0.3202159906507797</v>
       </c>
       <c r="C2">
-        <v>0.02100517802172865</v>
+        <v>0.02100517802154883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="E2">
-        <v>0.2805148076345911</v>
+        <v>0.2805148124215775</v>
       </c>
       <c r="F2">
-        <v>0.3627034886280088</v>
+        <v>0.3627034934116036</v>
       </c>
     </row>
     <row r="3">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.07846015139494812</v>
+        <v>0.0784601513323952</v>
       </c>
       <c r="C3">
-        <v>0.007741021975271219</v>
+        <v>0.007741021929549781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -428,10 +428,10 @@
         </is>
       </c>
       <c r="E3">
-        <v>0.06456781039231102</v>
+        <v>0.06456781040567089</v>
       </c>
       <c r="F3">
-        <v>0.09503787151881539</v>
+        <v>0.09503787135097823</v>
       </c>
     </row>
     <row r="4">
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.02939261874278487</v>
+        <v>0.02939261859217865</v>
       </c>
       <c r="C4">
-        <v>0.003395010569150395</v>
+        <v>0.003395010545814493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="E4">
-        <v>0.0234210414303495</v>
+        <v>0.02342104131976481</v>
       </c>
       <c r="F4">
-        <v>0.03682932793207761</v>
+        <v>0.03682932772905201</v>
       </c>
     </row>
     <row r="5">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.2528774705910948</v>
+        <v>0.2528774696516128</v>
       </c>
       <c r="C5">
-        <v>0.01769598647782222</v>
+        <v>0.01769598631797412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -476,10 +476,10 @@
         </is>
       </c>
       <c r="E5">
-        <v>0.219787997617846</v>
+        <v>0.2197879969721249</v>
       </c>
       <c r="F5">
-        <v>0.2891026923872292</v>
+        <v>0.2891026911171593</v>
       </c>
     </row>
     <row r="6">
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.502974312762457</v>
+        <v>0.5029743087816263</v>
       </c>
       <c r="C6">
-        <v>0.02259549119670388</v>
+        <v>0.02259549101829171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="E6">
-        <v>0.4587801949260394</v>
+        <v>0.4587801913236075</v>
       </c>
       <c r="F6">
-        <v>0.5471220042577367</v>
+        <v>0.5471219999613781</v>
       </c>
     </row>
   </sheetData>

--- a/data/stats/supp_tables/fallcover-cc-cc-estimates.xlsx
+++ b/data/stats/supp_tables/fallcover-cc-cc-estimates.xlsx
@@ -11,6 +11,47 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+  <si>
+    <t>cctrt_id</t>
+  </si>
+  <si>
+    <t>response</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>asymp.LCL</t>
+  </si>
+  <si>
+    <t>asymp.UCL</t>
+  </si>
+  <si>
+    <t>mix_E</t>
+  </si>
+  <si>
+    <t>Inf</t>
+  </si>
+  <si>
+    <t>mix_M</t>
+  </si>
+  <si>
+    <t>nocc</t>
+  </si>
+  <si>
+    <t>rad_L</t>
+  </si>
+  <si>
+    <t>rad_M</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,156 +395,124 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>cctrt_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>response</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>asymp.LCL</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>asymp.UCL</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mix_E</t>
-        </is>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>0.3202159906507797</v>
+        <v>0.3202159915118195</v>
       </c>
       <c r="C2">
-        <v>0.02100517802154883</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02100517802246322</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>0.2805148124215775</v>
+        <v>0.280514813272545</v>
       </c>
       <c r="F2">
-        <v>0.3627034934116036</v>
+        <v>0.3627034942656566</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mix_M</t>
-        </is>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>0.0784601513323952</v>
+        <v>0.07846015130859005</v>
       </c>
       <c r="C3">
-        <v>0.007741021929549781</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.007741021920886122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>0.06456781040567089</v>
+        <v>0.06456781039645197</v>
       </c>
       <c r="F3">
-        <v>0.09503787135097823</v>
+        <v>0.09503787130747325</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>nocc</t>
-        </is>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>0.02939261859217865</v>
+        <v>0.02939261856505664</v>
       </c>
       <c r="C4">
-        <v>0.003395010545814493</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.003395010541754007</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>0.02342104131976481</v>
+        <v>0.02342104129962701</v>
       </c>
       <c r="F4">
-        <v>0.03682932772905201</v>
+        <v>0.03682932769283601</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>rad_L</t>
-        </is>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>0.2528774696516128</v>
+        <v>0.2528774694613019</v>
       </c>
       <c r="C5">
-        <v>0.01769598631797412</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.01769598628968355</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>0.2197879969721249</v>
+        <v>0.2197879968340454</v>
       </c>
       <c r="F5">
-        <v>0.2891026911171593</v>
+        <v>0.2891026908686011</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>rad_M</t>
-        </is>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>0.5029743087816263</v>
+        <v>0.5029743080595921</v>
       </c>
       <c r="C6">
-        <v>0.02259549101829171</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02259549098781189</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>0.4587801913236075</v>
+        <v>0.4587801906665462</v>
       </c>
       <c r="F6">
-        <v>0.5471219999613781</v>
+        <v>0.5471219991857665</v>
       </c>
     </row>
   </sheetData>
